--- a/pipeline/credit_rating/output/visrating_xhtn_20261001.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20261001.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -654,7 +654,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -877,7 +877,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q111" s="1" t="n">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q112" s="1" t="n">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q113" s="1" t="n">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:10</t>
+          <t>2026-10-01 15:39:33</t>
         </is>
       </c>
       <c r="Q114" s="1" t="n">
